--- a/sources/metaPee/combined/provisional_ui/subexposure_views/no/Plot/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
+++ b/sources/metaPee/combined/provisional_ui/subexposure_views/no/Plot/exposures_meta_analysis_renal_cell_carcinoma_dietary.xlsx
@@ -802,22 +802,22 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.7291323597580593</v>
+        <v>0.7171286688639856</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.6668434288349496</v>
+        <v>0.6528551478261688</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.7972396143652196</v>
+        <v>0.7877299113272275</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.5433609689648237</v>
+        <v>0.5273554843225526</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.9784177156839051</v>
+        <v>0.975193286113776</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
@@ -1376,86 +1376,86 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>processed_meat_intake</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.1</v>
+        <v>1.148894298164554</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.87</v>
+        <v>0.9362244820588583</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
+        <v>1.410014516884722</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.6286522322</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>2.099663439889117</v>
+      </c>
       <c r="H29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="2" t="n">
-        <v>120852</v>
+        <v>1766660</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>485</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>processed_meat_intake</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1.148894298164554</v>
+        <v>1.178214315092722</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.9362244820588583</v>
+        <v>0.5980385872137474</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1.410014516884722</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0.6286522322</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>2.099663439889117</v>
-      </c>
+        <v>2.321468593851135</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="2" t="n">
-        <v>1766660</v>
+        <v>4597</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>5212</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.178214315092722</v>
+        <v>1.2</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.5980385872137474</v>
+        <v>0.92</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2.321468593851135</v>
+        <v>1.58</v>
       </c>
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr"/>
@@ -1464,29 +1464,29 @@
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
-        <v>4597</v>
+        <v>1811</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.227525064963178</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.92</v>
+        <v>0.5259232444453181</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1.58</v>
+        <v>2.865377201601115</v>
       </c>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr"/>
@@ -1495,29 +1495,29 @@
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="2" t="n">
-        <v>1811</v>
+        <v>4597</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1.227525064963178</v>
+        <v>1.28</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.5259232444453181</v>
+        <v>0.87</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2.865377201601115</v>
+        <v>1.9</v>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>4597</v>
+        <v>120852</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1909</v>
+        <v>485</v>
       </c>
     </row>
     <row r="34">
